--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.165.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.165.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.165.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.165.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y51"/>
+  <dimension ref="A1:Y57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -605,16 +605,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L11: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Re-Engrossment â€” in what cases</t>
+          <t>L40: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Re-Engrossment â€”in what cases</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]158</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]158</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L13: isolated marker/symbol line :: 158</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L38: isolated marker/symbol line :: #</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]158</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -636,7 +640,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L122: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Application how made</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -657,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>106</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -668,12 +676,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L21: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 22 â€” 23</t>
+          <t>L50: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 22â€”23</t>
+          <t>L97: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -685,7 +693,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L40: isolated marker/symbol line :: 20</t>
+          <t>L38: isolated marker/symbol line :: #</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -727,12 +735,12 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L57: stray/suspicious non-ASCII glyph(s): U+5341 CJK UNIFIED IDEOGRAPH-5341 | isolated marker/symbol line :: 十</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 23â€”113</t>
+          <t>L99: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -744,7 +752,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L42: isolated marker/symbol line :: 21</t>
+          <t>L40: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -784,14 +792,10 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 23 â€” 113</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L107: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: May be confined to short Statement . . •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -803,7 +807,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L46: isolated marker/symbol line :: 22</t>
+          <t>L42: isolated marker/symbol line :: 21</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -843,26 +847,22 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å��</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L99: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L122: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Application how made</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L22: isolated marker/symbol line :: 23</t>
+          <t>L21: symbol-only separator/garbage line :: 22 — 23</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L50: isolated marker/symbol line :: #</t>
+          <t>L46: isolated marker/symbol line :: 22</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -905,19 +905,19 @@
       <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: May be confined to short Statement . . â€¢</t>
+          <t>L130: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L24: isolated marker/symbol line :: 23</t>
+          <t>L22: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L52: isolated marker/symbol line :: 23</t>
+          <t>L48: symbol-only separator/garbage line :: 22—23</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -960,19 +960,19 @@
       <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L122: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Application how made</t>
+          <t>L150: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L31: isolated marker/symbol line :: C</t>
+          <t>L24: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L54: isolated marker/symbol line :: 23</t>
+          <t>L50: isolated marker/symbol line :: #</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1011,19 +1011,19 @@
       <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L130: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L152: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L32: isolated marker/symbol line :: N</t>
+          <t>L31: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L56: isolated marker/symbol line :: 24</t>
+          <t>L52: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1062,19 +1062,19 @@
       <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L148: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 41â€”42</t>
+          <t>L154: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: Y</t>
+          <t>L32: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L58: isolated marker/symbol line :: 24</t>
+          <t>L54: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1113,19 +1113,19 @@
       <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L150: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L165: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • / 42</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L45: isolated marker/symbol line :: .</t>
+          <t>L39: isolated marker/symbol line :: Y</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: H(</t>
+          <t>L56: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1164,19 +1164,19 @@
       <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L152: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L169: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: ••</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L40: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L66: isolated marker/symbol line :: C&lt;</t>
+          <t>L58: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1215,19 +1215,19 @@
       <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L154: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L171: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L51: isolated marker/symbol line :: 24</t>
+          <t>L45: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: N</t>
+          <t>L60: symbol-only separator/garbage line :: 23—113</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1266,19 +1266,19 @@
       <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L165: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ / 42</t>
+          <t>L192: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L53: isolated marker/symbol line :: 24</t>
+          <t>L50: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L75: isolated marker/symbol line :: T</t>
+          <t>L63: isolated marker/symbol line :: H(</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1317,19 +1317,19 @@
       <c r="J15" s="1" t="inlineStr"/>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>L169: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢â€¢</t>
+          <t>L194: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L56: isolated marker/symbol line :: 110</t>
+          <t>L51: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: O</t>
+          <t>L66: isolated marker/symbol line :: C&lt;</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1366,21 +1366,17 @@
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L171: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å��</t>
+          <t>L53: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: E</t>
+          <t>L67: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1417,21 +1413,17 @@
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L192: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L58: isolated marker/symbol line :: 40</t>
+          <t>L55: symbol-only separator/garbage line :: 23 — 113</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L78: isolated marker/symbol line :: E</t>
+          <t>L75: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1456,21 +1448,17 @@
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L194: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L59: isolated marker/symbol line :: 40</t>
+          <t>L56: isolated marker/symbol line :: 110</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: P</t>
+          <t>L76: isolated marker/symbol line :: O</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1500,12 +1488,12 @@
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L60: isolated marker/symbol line :: 40</t>
+          <t>L57: stray/suspicious non-ASCII glyph(s): U+5341 CJK UNIFIED IDEOGRAPH-5341 | isolated marker/symbol line :: 十</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: P</t>
+          <t>L77: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1535,12 +1523,12 @@
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L61: isolated marker/symbol line :: 41</t>
+          <t>L58: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L87: isolated marker/symbol line :: T</t>
+          <t>L78: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1570,12 +1558,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L62: isolated marker/symbol line :: 41</t>
+          <t>L59: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L89: isolated marker/symbol line :: -</t>
+          <t>L80: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1605,12 +1593,12 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: 41</t>
+          <t>L60: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L91: isolated marker/symbol line :: 0</t>
+          <t>L84: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1640,12 +1628,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: O</t>
+          <t>L61: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L93: isolated marker/symbol line :: N</t>
+          <t>L87: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1675,12 +1663,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: T</t>
+          <t>L62: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L94: isolated marker/symbol line :: A</t>
+          <t>L89: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1710,12 +1698,12 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L68: isolated marker/symbol line :: 0</t>
+          <t>L63: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: s</t>
+          <t>L91: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1745,12 +1733,12 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: O</t>
+          <t>L65: isolated marker/symbol line :: O</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L93: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1780,12 +1768,12 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: E</t>
+          <t>L67: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L99: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L94: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1815,12 +1803,12 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L71: isolated marker/symbol line :: E</t>
+          <t>L68: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: f</t>
+          <t>L95: isolated marker/symbol line :: s</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1850,12 +1838,12 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L72: isolated marker/symbol line :: P</t>
+          <t>L69: isolated marker/symbol line :: O</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L126: isolated marker/symbol line :: 110</t>
+          <t>L97: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1885,12 +1873,12 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L74: isolated marker/symbol line :: P</t>
+          <t>L70: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L128: isolated marker/symbol line :: &gt;</t>
+          <t>L99: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1920,12 +1908,12 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: T</t>
+          <t>L71: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L130: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L124: isolated marker/symbol line :: f</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1955,12 +1943,12 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: 4</t>
+          <t>L72: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L132: isolated marker/symbol line :: 40</t>
+          <t>L126: isolated marker/symbol line :: 110</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -1990,12 +1978,12 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L78: isolated marker/symbol line :: 0</t>
+          <t>L74: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L134: isolated marker/symbol line :: 40</t>
+          <t>L128: isolated marker/symbol line :: &gt;</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2025,12 +2013,12 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L79: isolated marker/symbol line :: N</t>
+          <t>L76: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L136: isolated marker/symbol line :: 40</t>
+          <t>L130: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2060,12 +2048,12 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: A</t>
+          <t>L77: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L138: symbol-only separator/garbage line :: 41.</t>
+          <t>L132: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2095,12 +2083,12 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L85: isolated marker/symbol line :: r</t>
+          <t>L78: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L140: isolated marker/symbol line :: 41</t>
+          <t>L134: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2130,12 +2118,12 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L93: isolated marker/symbol line :: 41</t>
+          <t>L79: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L142: isolated marker/symbol line :: 41</t>
+          <t>L136: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2165,12 +2153,12 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L94: isolated marker/symbol line :: 41</t>
+          <t>L80: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L144: symbol-only separator/garbage line :: . 41</t>
+          <t>L138: symbol-only separator/garbage line :: 41.</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2200,12 +2188,12 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L95: symbol-only separator/garbage line :: 41-42</t>
+          <t>L85: isolated marker/symbol line :: r</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L146: isolated marker/symbol line :: 41</t>
+          <t>L140: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
@@ -2235,12 +2223,12 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L97: isolated marker/symbol line :: 42</t>
+          <t>L93: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L150: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L142: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
@@ -2270,12 +2258,12 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L98: isolated marker/symbol line :: 42</t>
+          <t>L94: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L152: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L144: symbol-only separator/garbage line :: . 41</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
@@ -2305,12 +2293,12 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L99: isolated marker/symbol line :: 43</t>
+          <t>L95: symbol-only separator/garbage line :: 41-42</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L154: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L146: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
@@ -2340,12 +2328,12 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L100: isolated marker/symbol line :: 43</t>
+          <t>L97: isolated marker/symbol line :: 42</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L164: symbol-only separator/garbage line | localized OCR phrase divergence vs other OCR: "" vs "42 42 43X" :: 42 &gt;</t>
+          <t>L148: symbol-only separator/garbage line :: 41—42</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
@@ -2375,12 +2363,12 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L102: isolated marker/symbol line :: 43</t>
+          <t>L98: isolated marker/symbol line :: 42</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>L171: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L150: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr"/>
@@ -2410,12 +2398,12 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L104: isolated marker/symbol line :: 2</t>
+          <t>L99: isolated marker/symbol line :: 43</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L181: isolated marker/symbol line :: 4</t>
+          <t>L152: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
@@ -2445,12 +2433,12 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: 6</t>
+          <t>L100: isolated marker/symbol line :: 43</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>L183: isolated marker/symbol line :: 1</t>
+          <t>L154: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr"/>
@@ -2478,10 +2466,14 @@
       <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
-      <c r="N47" s="1" t="inlineStr"/>
+      <c r="N47" s="1" t="inlineStr">
+        <is>
+          <t>L102: isolated marker/symbol line :: 43</t>
+        </is>
+      </c>
       <c r="O47" s="1" t="inlineStr">
         <is>
-          <t>L184: isolated marker/symbol line :: I</t>
+          <t>L164: symbol-only separator/garbage line | localized OCR phrase divergence vs other OCR: "" vs "42 42 43X" :: 42 &gt;</t>
         </is>
       </c>
       <c r="P47" s="1" t="inlineStr"/>
@@ -2509,10 +2501,14 @@
       <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
-      <c r="N48" s="1" t="inlineStr"/>
+      <c r="N48" s="1" t="inlineStr">
+        <is>
+          <t>L104: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
-          <t>L186: isolated marker/symbol line :: 1</t>
+          <t>L165: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • / 42</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr"/>
@@ -2540,10 +2536,14 @@
       <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
-      <c r="N49" s="1" t="inlineStr"/>
+      <c r="N49" s="1" t="inlineStr">
+        <is>
+          <t>L105: isolated marker/symbol line :: 6</t>
+        </is>
+      </c>
       <c r="O49" s="1" t="inlineStr">
         <is>
-          <t>L188: isolated marker/symbol line :: 43</t>
+          <t>L169: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: ••</t>
         </is>
       </c>
       <c r="P49" s="1" t="inlineStr"/>
@@ -2574,7 +2574,7 @@
       <c r="N50" s="1" t="inlineStr"/>
       <c r="O50" s="1" t="inlineStr">
         <is>
-          <t>L192: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L171: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P50" s="1" t="inlineStr"/>
@@ -2605,7 +2605,7 @@
       <c r="N51" s="1" t="inlineStr"/>
       <c r="O51" s="1" t="inlineStr">
         <is>
-          <t>L194: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L181: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="P51" s="1" t="inlineStr"/>
@@ -2619,6 +2619,192 @@
       <c r="X51" s="1" t="inlineStr"/>
       <c r="Y51" s="1" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr"/>
+      <c r="B52" s="1" t="inlineStr"/>
+      <c r="C52" s="1" t="inlineStr"/>
+      <c r="D52" s="1" t="inlineStr"/>
+      <c r="E52" s="1" t="inlineStr"/>
+      <c r="F52" s="1" t="inlineStr"/>
+      <c r="G52" s="1" t="inlineStr"/>
+      <c r="H52" s="1" t="inlineStr"/>
+      <c r="I52" s="1" t="inlineStr"/>
+      <c r="J52" s="1" t="inlineStr"/>
+      <c r="K52" s="1" t="inlineStr"/>
+      <c r="L52" s="1" t="inlineStr"/>
+      <c r="M52" s="1" t="inlineStr"/>
+      <c r="N52" s="1" t="inlineStr"/>
+      <c r="O52" s="1" t="inlineStr">
+        <is>
+          <t>L183: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="P52" s="1" t="inlineStr"/>
+      <c r="Q52" s="1" t="inlineStr"/>
+      <c r="R52" s="1" t="inlineStr"/>
+      <c r="S52" s="1" t="inlineStr"/>
+      <c r="T52" s="1" t="inlineStr"/>
+      <c r="U52" s="1" t="inlineStr"/>
+      <c r="V52" s="1" t="inlineStr"/>
+      <c r="W52" s="1" t="inlineStr"/>
+      <c r="X52" s="1" t="inlineStr"/>
+      <c r="Y52" s="1" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr"/>
+      <c r="B53" s="1" t="inlineStr"/>
+      <c r="C53" s="1" t="inlineStr"/>
+      <c r="D53" s="1" t="inlineStr"/>
+      <c r="E53" s="1" t="inlineStr"/>
+      <c r="F53" s="1" t="inlineStr"/>
+      <c r="G53" s="1" t="inlineStr"/>
+      <c r="H53" s="1" t="inlineStr"/>
+      <c r="I53" s="1" t="inlineStr"/>
+      <c r="J53" s="1" t="inlineStr"/>
+      <c r="K53" s="1" t="inlineStr"/>
+      <c r="L53" s="1" t="inlineStr"/>
+      <c r="M53" s="1" t="inlineStr"/>
+      <c r="N53" s="1" t="inlineStr"/>
+      <c r="O53" s="1" t="inlineStr">
+        <is>
+          <t>L184: isolated marker/symbol line :: I</t>
+        </is>
+      </c>
+      <c r="P53" s="1" t="inlineStr"/>
+      <c r="Q53" s="1" t="inlineStr"/>
+      <c r="R53" s="1" t="inlineStr"/>
+      <c r="S53" s="1" t="inlineStr"/>
+      <c r="T53" s="1" t="inlineStr"/>
+      <c r="U53" s="1" t="inlineStr"/>
+      <c r="V53" s="1" t="inlineStr"/>
+      <c r="W53" s="1" t="inlineStr"/>
+      <c r="X53" s="1" t="inlineStr"/>
+      <c r="Y53" s="1" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr"/>
+      <c r="B54" s="1" t="inlineStr"/>
+      <c r="C54" s="1" t="inlineStr"/>
+      <c r="D54" s="1" t="inlineStr"/>
+      <c r="E54" s="1" t="inlineStr"/>
+      <c r="F54" s="1" t="inlineStr"/>
+      <c r="G54" s="1" t="inlineStr"/>
+      <c r="H54" s="1" t="inlineStr"/>
+      <c r="I54" s="1" t="inlineStr"/>
+      <c r="J54" s="1" t="inlineStr"/>
+      <c r="K54" s="1" t="inlineStr"/>
+      <c r="L54" s="1" t="inlineStr"/>
+      <c r="M54" s="1" t="inlineStr"/>
+      <c r="N54" s="1" t="inlineStr"/>
+      <c r="O54" s="1" t="inlineStr">
+        <is>
+          <t>L186: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="P54" s="1" t="inlineStr"/>
+      <c r="Q54" s="1" t="inlineStr"/>
+      <c r="R54" s="1" t="inlineStr"/>
+      <c r="S54" s="1" t="inlineStr"/>
+      <c r="T54" s="1" t="inlineStr"/>
+      <c r="U54" s="1" t="inlineStr"/>
+      <c r="V54" s="1" t="inlineStr"/>
+      <c r="W54" s="1" t="inlineStr"/>
+      <c r="X54" s="1" t="inlineStr"/>
+      <c r="Y54" s="1" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr"/>
+      <c r="B55" s="1" t="inlineStr"/>
+      <c r="C55" s="1" t="inlineStr"/>
+      <c r="D55" s="1" t="inlineStr"/>
+      <c r="E55" s="1" t="inlineStr"/>
+      <c r="F55" s="1" t="inlineStr"/>
+      <c r="G55" s="1" t="inlineStr"/>
+      <c r="H55" s="1" t="inlineStr"/>
+      <c r="I55" s="1" t="inlineStr"/>
+      <c r="J55" s="1" t="inlineStr"/>
+      <c r="K55" s="1" t="inlineStr"/>
+      <c r="L55" s="1" t="inlineStr"/>
+      <c r="M55" s="1" t="inlineStr"/>
+      <c r="N55" s="1" t="inlineStr"/>
+      <c r="O55" s="1" t="inlineStr">
+        <is>
+          <t>L188: isolated marker/symbol line :: 43</t>
+        </is>
+      </c>
+      <c r="P55" s="1" t="inlineStr"/>
+      <c r="Q55" s="1" t="inlineStr"/>
+      <c r="R55" s="1" t="inlineStr"/>
+      <c r="S55" s="1" t="inlineStr"/>
+      <c r="T55" s="1" t="inlineStr"/>
+      <c r="U55" s="1" t="inlineStr"/>
+      <c r="V55" s="1" t="inlineStr"/>
+      <c r="W55" s="1" t="inlineStr"/>
+      <c r="X55" s="1" t="inlineStr"/>
+      <c r="Y55" s="1" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr"/>
+      <c r="B56" s="1" t="inlineStr"/>
+      <c r="C56" s="1" t="inlineStr"/>
+      <c r="D56" s="1" t="inlineStr"/>
+      <c r="E56" s="1" t="inlineStr"/>
+      <c r="F56" s="1" t="inlineStr"/>
+      <c r="G56" s="1" t="inlineStr"/>
+      <c r="H56" s="1" t="inlineStr"/>
+      <c r="I56" s="1" t="inlineStr"/>
+      <c r="J56" s="1" t="inlineStr"/>
+      <c r="K56" s="1" t="inlineStr"/>
+      <c r="L56" s="1" t="inlineStr"/>
+      <c r="M56" s="1" t="inlineStr"/>
+      <c r="N56" s="1" t="inlineStr"/>
+      <c r="O56" s="1" t="inlineStr">
+        <is>
+          <t>L192: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
+      <c r="P56" s="1" t="inlineStr"/>
+      <c r="Q56" s="1" t="inlineStr"/>
+      <c r="R56" s="1" t="inlineStr"/>
+      <c r="S56" s="1" t="inlineStr"/>
+      <c r="T56" s="1" t="inlineStr"/>
+      <c r="U56" s="1" t="inlineStr"/>
+      <c r="V56" s="1" t="inlineStr"/>
+      <c r="W56" s="1" t="inlineStr"/>
+      <c r="X56" s="1" t="inlineStr"/>
+      <c r="Y56" s="1" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr"/>
+      <c r="B57" s="1" t="inlineStr"/>
+      <c r="C57" s="1" t="inlineStr"/>
+      <c r="D57" s="1" t="inlineStr"/>
+      <c r="E57" s="1" t="inlineStr"/>
+      <c r="F57" s="1" t="inlineStr"/>
+      <c r="G57" s="1" t="inlineStr"/>
+      <c r="H57" s="1" t="inlineStr"/>
+      <c r="I57" s="1" t="inlineStr"/>
+      <c r="J57" s="1" t="inlineStr"/>
+      <c r="K57" s="1" t="inlineStr"/>
+      <c r="L57" s="1" t="inlineStr"/>
+      <c r="M57" s="1" t="inlineStr"/>
+      <c r="N57" s="1" t="inlineStr"/>
+      <c r="O57" s="1" t="inlineStr">
+        <is>
+          <t>L194: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
+      <c r="P57" s="1" t="inlineStr"/>
+      <c r="Q57" s="1" t="inlineStr"/>
+      <c r="R57" s="1" t="inlineStr"/>
+      <c r="S57" s="1" t="inlineStr"/>
+      <c r="T57" s="1" t="inlineStr"/>
+      <c r="U57" s="1" t="inlineStr"/>
+      <c r="V57" s="1" t="inlineStr"/>
+      <c r="W57" s="1" t="inlineStr"/>
+      <c r="X57" s="1" t="inlineStr"/>
+      <c r="Y57" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
